--- a/Components.xlsx
+++ b/Components.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nuwildcat-my.sharepoint.com/personal/org0708_ads_northwestern_edu/Documents/Northwestern/Extracurricular/hardware/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="122" documentId="11_F25DC773A252ABDACC10485809DA5EF65ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6BDB55DC-3389-4955-855E-B5C1862F1073}"/>
+  <xr:revisionPtr revIDLastSave="171" documentId="11_F25DC773A252ABDACC10485809DA5EF65ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF7EC096-9728-4705-B35C-A892A0B799CB}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="12196" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="60">
   <si>
     <t>Component</t>
   </si>
@@ -124,6 +124,87 @@
   </si>
   <si>
     <t>AOD21357</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>Transceiver</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>TJA1051T/3</t>
+  </si>
+  <si>
+    <t>568-13277-2-ND</t>
+  </si>
+  <si>
+    <t>NXP USA Inc.</t>
+  </si>
+  <si>
+    <t>Custom</t>
+  </si>
+  <si>
+    <t>1/1 Transceiver Half CANbus 8-SO</t>
+  </si>
+  <si>
+    <t>TVS</t>
+  </si>
+  <si>
+    <t>1727-3891-2-ND</t>
+  </si>
+  <si>
+    <t>Nexperia USA Inc.</t>
+  </si>
+  <si>
+    <t>PESD2CAN,215</t>
+  </si>
+  <si>
+    <t>41V Clamp 5A (8/20µs) Ipp Tvs Diode Surface Mount TO-236AB</t>
+  </si>
+  <si>
+    <t>Surface Mount TO-236AB</t>
+  </si>
+  <si>
+    <t>CMC</t>
+  </si>
+  <si>
+    <t>U6</t>
+  </si>
+  <si>
+    <t>U5</t>
+  </si>
+  <si>
+    <t>ACT45B-101-2P-TL003</t>
+  </si>
+  <si>
+    <t>445-3959-2-ND</t>
+  </si>
+  <si>
+    <t>TDK</t>
+  </si>
+  <si>
+    <t>100 µH @ 100 kHz 2 Line Common Mode Choke Surface Mount 5.8 kOhms @ 10 MHz 150mA DCR 2Ohm</t>
+  </si>
+  <si>
+    <t>Switch (CAN)</t>
+  </si>
+  <si>
+    <t>2223-DS01-254-L-01BE-ND</t>
+  </si>
+  <si>
+    <t>Same Sky (Formerly CUI Devices)</t>
+  </si>
+  <si>
+    <t>DS01-254-L-01BE</t>
+  </si>
+  <si>
+    <t>Dip Switch SPST 1 Position Through Hole Slide (Standard) Actuator 25mA 24VDC</t>
   </si>
 </sst>
 </file>
@@ -201,7 +282,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -216,6 +297,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -507,7 +592,7 @@
     <col min="5" max="5" width="14.19921875" customWidth="1"/>
     <col min="6" max="6" width="31.1328125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.1328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="31.06640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="52.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="11" width="14.19921875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -591,6 +676,9 @@
       <c r="B5" t="s">
         <v>12</v>
       </c>
+      <c r="C5" t="s">
+        <v>35</v>
+      </c>
       <c r="D5" s="2"/>
       <c r="E5" s="3" t="s">
         <v>19</v>
@@ -643,8 +731,121 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="H11" s="1"/>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A8" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I8">
+        <v>2</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="B9" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="B10" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="I10">
+        <v>2</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="B11" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" t="s">
+        <v>57</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I11">
+        <v>4</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -653,6 +854,10 @@
     <hyperlink ref="G5" r:id="rId3" display="https://www.digikey.com/en/products/filter/fuses/1206-3216-metric/139?s=N4IgjCBcpgbFoDGUBmBDANgZwKYBoQA3AOygBcAnAV3xAHsoBtEADgGYB2MCAXQIAcyUEAGVKAS2IBzEAF95QA" xr:uid="{98185761-E669-4D71-BFFE-742816C993DF}"/>
     <hyperlink ref="J5" r:id="rId4" xr:uid="{BB308056-6C69-4446-ABC1-0CEE27EE8208}"/>
     <hyperlink ref="F4" r:id="rId5" display="https://www.digikey.com/en/supplier-centers/alpha-and-omega-semiconductor" xr:uid="{B79ECA54-82EC-40BB-888A-002F6800B9B3}"/>
+    <hyperlink ref="J8" r:id="rId6" xr:uid="{11F395D0-5504-489D-8656-EE1A54C23DDA}"/>
+    <hyperlink ref="J9" r:id="rId7" xr:uid="{798877DA-B291-4CC0-84A7-001B9134CF0B}"/>
+    <hyperlink ref="J10" r:id="rId8" xr:uid="{00E66CDD-5400-4FE1-89A5-0B9266D05039}"/>
+    <hyperlink ref="J11" r:id="rId9" xr:uid="{9BE63AE3-6695-42BA-8E8F-2E98D962A63D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Components.xlsx
+++ b/Components.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nuwildcat-my.sharepoint.com/personal/org0708_ads_northwestern_edu/Documents/Northwestern/Extracurricular/hardware/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="171" documentId="11_F25DC773A252ABDACC10485809DA5EF65ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF7EC096-9728-4705-B35C-A892A0B799CB}"/>
+  <xr:revisionPtr revIDLastSave="204" documentId="11_F25DC773A252ABDACC10485809DA5EF65ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9468D61-9264-4919-89F4-AD203C41BB0F}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="12196" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="72">
   <si>
     <t>Component</t>
   </si>
@@ -205,6 +205,42 @@
   </si>
   <si>
     <t>Dip Switch SPST 1 Position Through Hole Slide (Standard) Actuator 25mA 24VDC</t>
+  </si>
+  <si>
+    <t>MCU</t>
+  </si>
+  <si>
+    <t>Hat pins</t>
+  </si>
+  <si>
+    <t>SW1 / 2</t>
+  </si>
+  <si>
+    <t>1528-2831-ND</t>
+  </si>
+  <si>
+    <t>Adafruit Industries LLC</t>
+  </si>
+  <si>
+    <t>2X20 SOCKET RISER HEADER FOR RPI</t>
+  </si>
+  <si>
+    <t>MCP2515</t>
+  </si>
+  <si>
+    <t>MCP2515-I/SO-ND</t>
+  </si>
+  <si>
+    <t>MCP2515-I/SO</t>
+  </si>
+  <si>
+    <t>Microchip Technology</t>
+  </si>
+  <si>
+    <t>IC CAN CONTROLLER W/SPI 18SOIC</t>
+  </si>
+  <si>
+    <t>Crystal</t>
   </si>
 </sst>
 </file>
@@ -583,7 +619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:L11"/>
+  <dimension ref="A2:L15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="14.19921875" customWidth="1"/>
@@ -828,6 +864,9 @@
       <c r="B11" s="9" t="s">
         <v>55</v>
       </c>
+      <c r="C11" t="s">
+        <v>62</v>
+      </c>
       <c r="D11" t="s">
         <v>58</v>
       </c>
@@ -846,6 +885,58 @@
       <c r="J11" s="4" t="s">
         <v>7</v>
       </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A13" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13">
+        <v>4079</v>
+      </c>
+      <c r="E13" t="s">
+        <v>63</v>
+      </c>
+      <c r="F13" t="s">
+        <v>64</v>
+      </c>
+      <c r="H13" t="s">
+        <v>65</v>
+      </c>
+      <c r="I13">
+        <v>2</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="B14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" t="s">
+        <v>67</v>
+      </c>
+      <c r="F14" t="s">
+        <v>69</v>
+      </c>
+      <c r="H14" t="s">
+        <v>70</v>
+      </c>
+      <c r="I14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="B15" t="s">
+        <v>71</v>
+      </c>
+      <c r="J15" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -858,6 +949,7 @@
     <hyperlink ref="J9" r:id="rId7" xr:uid="{798877DA-B291-4CC0-84A7-001B9134CF0B}"/>
     <hyperlink ref="J10" r:id="rId8" xr:uid="{00E66CDD-5400-4FE1-89A5-0B9266D05039}"/>
     <hyperlink ref="J11" r:id="rId9" xr:uid="{9BE63AE3-6695-42BA-8E8F-2E98D962A63D}"/>
+    <hyperlink ref="J13" r:id="rId10" xr:uid="{E0D90F7C-094F-47C4-9689-4F38ABBDE890}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Components.xlsx
+++ b/Components.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nuwildcat-my.sharepoint.com/personal/org0708_ads_northwestern_edu/Documents/Northwestern/Extracurricular/hardware/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="204" documentId="11_F25DC773A252ABDACC10485809DA5EF65ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9468D61-9264-4919-89F4-AD203C41BB0F}"/>
+  <xr:revisionPtr revIDLastSave="221" documentId="11_F25DC773A252ABDACC10485809DA5EF65ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E71FEC77-4CD1-43D0-AD9B-496F73B709CB}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="12196" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="82">
   <si>
     <t>Component</t>
   </si>
@@ -241,6 +241,36 @@
   </si>
   <si>
     <t>Crystal</t>
+  </si>
+  <si>
+    <t>Y1</t>
+  </si>
+  <si>
+    <t>535-10630-2-ND</t>
+  </si>
+  <si>
+    <t>Abracon LLC</t>
+  </si>
+  <si>
+    <t>CRYSTAL 8.0000MHZ 18PF SMD</t>
+  </si>
+  <si>
+    <t>2-SMD,</t>
+  </si>
+  <si>
+    <t>ABM3-8.000MHZ-D2Y-T</t>
+  </si>
+  <si>
+    <t>J1</t>
+  </si>
+  <si>
+    <t>U3</t>
+  </si>
+  <si>
+    <t>22pF Cap (crystal)</t>
+  </si>
+  <si>
+    <t>Resistor</t>
   </si>
 </sst>
 </file>
@@ -619,7 +649,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:L15"/>
+  <dimension ref="A2:L22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="14.19921875" customWidth="1"/>
@@ -886,57 +916,102 @@
         <v>7</v>
       </c>
     </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="B12" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A13" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B13" t="s">
-        <v>61</v>
-      </c>
-      <c r="D13">
-        <v>4079</v>
-      </c>
-      <c r="E13" t="s">
-        <v>63</v>
-      </c>
-      <c r="F13" t="s">
-        <v>64</v>
-      </c>
-      <c r="H13" t="s">
-        <v>65</v>
-      </c>
-      <c r="I13">
-        <v>2</v>
+      <c r="B13" s="9" t="s">
+        <v>81</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B14" t="s">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A20" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20">
+        <v>4079</v>
+      </c>
+      <c r="E20" t="s">
+        <v>63</v>
+      </c>
+      <c r="F20" t="s">
+        <v>64</v>
+      </c>
+      <c r="H20" t="s">
+        <v>65</v>
+      </c>
+      <c r="I20">
+        <v>2</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="B21" t="s">
         <v>66</v>
       </c>
-      <c r="D14" t="s">
+      <c r="C21" t="s">
+        <v>79</v>
+      </c>
+      <c r="D21" t="s">
         <v>68</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E21" t="s">
         <v>67</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F21" t="s">
         <v>69</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H21" t="s">
         <v>70</v>
       </c>
-      <c r="I14">
+      <c r="I21">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B15" t="s">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="B22" t="s">
         <v>71</v>
       </c>
-      <c r="J15" s="4"/>
+      <c r="C22" t="s">
+        <v>72</v>
+      </c>
+      <c r="D22" t="s">
+        <v>77</v>
+      </c>
+      <c r="E22" t="s">
+        <v>73</v>
+      </c>
+      <c r="F22" t="s">
+        <v>74</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H22" t="s">
+        <v>75</v>
+      </c>
+      <c r="I22">
+        <v>2</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -949,8 +1024,12 @@
     <hyperlink ref="J9" r:id="rId7" xr:uid="{798877DA-B291-4CC0-84A7-001B9134CF0B}"/>
     <hyperlink ref="J10" r:id="rId8" xr:uid="{00E66CDD-5400-4FE1-89A5-0B9266D05039}"/>
     <hyperlink ref="J11" r:id="rId9" xr:uid="{9BE63AE3-6695-42BA-8E8F-2E98D962A63D}"/>
-    <hyperlink ref="J13" r:id="rId10" xr:uid="{E0D90F7C-094F-47C4-9689-4F38ABBDE890}"/>
+    <hyperlink ref="J20" r:id="rId10" xr:uid="{E0D90F7C-094F-47C4-9689-4F38ABBDE890}"/>
+    <hyperlink ref="J22" r:id="rId11" xr:uid="{CEE19911-DD7A-45AF-839A-7B0BEFDAB83D}"/>
+    <hyperlink ref="J12" r:id="rId12" xr:uid="{47204ACE-9606-4881-B595-BDDC0AF532F3}"/>
+    <hyperlink ref="J13" r:id="rId13" xr:uid="{930E413D-5037-4B2D-90BF-4D2E6AEE824F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId14"/>
 </worksheet>
 </file>
--- a/Components.xlsx
+++ b/Components.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nuwildcat-my.sharepoint.com/personal/org0708_ads_northwestern_edu/Documents/Northwestern/Extracurricular/hardware/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="221" documentId="11_F25DC773A252ABDACC10485809DA5EF65ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E71FEC77-4CD1-43D0-AD9B-496F73B709CB}"/>
+  <xr:revisionPtr revIDLastSave="226" documentId="11_F25DC773A252ABDACC10485809DA5EF65ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C0FB696-3F0C-45B2-9788-BFA0B97EA8D5}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="12196" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="84">
   <si>
     <t>Component</t>
   </si>
@@ -271,6 +271,12 @@
   </si>
   <si>
     <t>Resistor</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>C10 / C11</t>
   </si>
 </sst>
 </file>
@@ -920,6 +926,12 @@
       <c r="B12" s="9" t="s">
         <v>80</v>
       </c>
+      <c r="C12" t="s">
+        <v>83</v>
+      </c>
+      <c r="I12">
+        <v>4</v>
+      </c>
       <c r="J12" s="4" t="s">
         <v>7</v>
       </c>
@@ -927,6 +939,12 @@
     <row r="13" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B13" s="9" t="s">
         <v>81</v>
+      </c>
+      <c r="C13" t="s">
+        <v>82</v>
+      </c>
+      <c r="I13">
+        <v>2</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>7</v>

--- a/Components.xlsx
+++ b/Components.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nuwildcat-my.sharepoint.com/personal/org0708_ads_northwestern_edu/Documents/Northwestern/Extracurricular/hardware/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="226" documentId="11_F25DC773A252ABDACC10485809DA5EF65ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C0FB696-3F0C-45B2-9788-BFA0B97EA8D5}"/>
+  <xr:revisionPtr revIDLastSave="233" documentId="11_F25DC773A252ABDACC10485809DA5EF65ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4649A450-41CD-4CD9-8E00-E0ED4DCA52DB}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="12196" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="84">
   <si>
     <t>Component</t>
   </si>
@@ -99,27 +99,15 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>U2</t>
-  </si>
-  <si>
-    <t>reviewed</t>
-  </si>
-  <si>
     <t>785-1833-1-ND</t>
   </si>
   <si>
     <t>Alpha &amp; Omega Semiconductor Inc.</t>
   </si>
   <si>
-    <t> Surface Mount TO-252 (DPAK)</t>
-  </si>
-  <si>
     <t>P-Channel 30 V 70A (Tc) 78W (Tc) Surface Mount TO-252 (DPAK)</t>
   </si>
   <si>
-    <t>lots of stats to review</t>
-  </si>
-  <si>
     <t>Manufacturer No.</t>
   </si>
   <si>
@@ -277,6 +265,18 @@
   </si>
   <si>
     <t>C10 / C11</t>
+  </si>
+  <si>
+    <t>Package_TO_SOT_SMD:TO-252-2</t>
+  </si>
+  <si>
+    <t>REVIEWED</t>
+  </si>
+  <si>
+    <t>PS1</t>
+  </si>
+  <si>
+    <t>TSR 3-2450N</t>
   </si>
 </sst>
 </file>
@@ -354,7 +354,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -370,7 +370,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -676,7 +675,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
         <v>2</v>
@@ -717,19 +716,19 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E4" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="I4">
         <v>2</v>
@@ -738,7 +737,7 @@
         <v>10</v>
       </c>
       <c r="K4" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="L4" t="s">
         <v>23</v>
@@ -749,7 +748,7 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="3" t="s">
@@ -771,7 +770,7 @@
         <v>7</v>
       </c>
       <c r="K5" t="s">
-        <v>25</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.45">
@@ -779,7 +778,10 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>82</v>
+      </c>
+      <c r="D6" t="s">
+        <v>83</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>15</v>
@@ -800,7 +802,7 @@
         <v>7</v>
       </c>
       <c r="K6" t="s">
-        <v>25</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.45">
@@ -808,28 +810,28 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="E8" t="s">
         <v>34</v>
       </c>
-      <c r="C8" t="s">
+      <c r="F8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="H8" t="s">
         <v>37</v>
-      </c>
-      <c r="E8" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" t="s">
-        <v>41</v>
       </c>
       <c r="I8">
         <v>2</v>
@@ -839,26 +841,26 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B9" s="9" t="s">
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" t="s">
         <v>42</v>
-      </c>
-      <c r="C9" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H9" t="s">
-        <v>46</v>
       </c>
       <c r="I9">
         <v>2</v>
@@ -868,26 +870,26 @@
       </c>
     </row>
     <row r="10" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="B10" s="9" t="s">
+      <c r="B10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" t="s">
         <v>48</v>
       </c>
-      <c r="C10" t="s">
+      <c r="F10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G10" t="s">
+        <v>36</v>
+      </c>
+      <c r="H10" s="9" t="s">
         <v>50</v>
-      </c>
-      <c r="D10" t="s">
-        <v>51</v>
-      </c>
-      <c r="E10" t="s">
-        <v>52</v>
-      </c>
-      <c r="F10" t="s">
-        <v>53</v>
-      </c>
-      <c r="G10" t="s">
-        <v>40</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>54</v>
       </c>
       <c r="I10">
         <v>2</v>
@@ -897,23 +899,23 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="B11" s="9" t="s">
+      <c r="B11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F11" t="s">
+        <v>53</v>
+      </c>
+      <c r="H11" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="C11" t="s">
-        <v>62</v>
-      </c>
-      <c r="D11" t="s">
-        <v>58</v>
-      </c>
-      <c r="E11" t="s">
-        <v>56</v>
-      </c>
-      <c r="F11" t="s">
-        <v>57</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="I11">
         <v>4</v>
@@ -923,11 +925,11 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B12" s="9" t="s">
-        <v>80</v>
+      <c r="B12" t="s">
+        <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="I12">
         <v>4</v>
@@ -937,11 +939,11 @@
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B13" s="9" t="s">
-        <v>81</v>
+      <c r="B13" t="s">
+        <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="I13">
         <v>2</v>
@@ -952,25 +954,25 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A20" s="6" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B20" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C20" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D20">
         <v>4079</v>
       </c>
       <c r="E20" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F20" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H20" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="I20">
         <v>2</v>
@@ -981,22 +983,22 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21" t="s">
+        <v>64</v>
+      </c>
+      <c r="E21" t="s">
+        <v>63</v>
+      </c>
+      <c r="F21" t="s">
+        <v>65</v>
+      </c>
+      <c r="H21" t="s">
         <v>66</v>
-      </c>
-      <c r="C21" t="s">
-        <v>79</v>
-      </c>
-      <c r="D21" t="s">
-        <v>68</v>
-      </c>
-      <c r="E21" t="s">
-        <v>67</v>
-      </c>
-      <c r="F21" t="s">
-        <v>69</v>
-      </c>
-      <c r="H21" t="s">
-        <v>70</v>
       </c>
       <c r="I21">
         <v>2</v>
@@ -1004,25 +1006,25 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" t="s">
+        <v>73</v>
+      </c>
+      <c r="E22" t="s">
+        <v>69</v>
+      </c>
+      <c r="F22" t="s">
+        <v>70</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H22" t="s">
         <v>71</v>
-      </c>
-      <c r="C22" t="s">
-        <v>72</v>
-      </c>
-      <c r="D22" t="s">
-        <v>77</v>
-      </c>
-      <c r="E22" t="s">
-        <v>73</v>
-      </c>
-      <c r="F22" t="s">
-        <v>74</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="H22" t="s">
-        <v>75</v>
       </c>
       <c r="I22">
         <v>2</v>

--- a/Components.xlsx
+++ b/Components.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nuwildcat-my.sharepoint.com/personal/org0708_ads_northwestern_edu/Documents/Northwestern/Extracurricular/hardware/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="233" documentId="11_F25DC773A252ABDACC10485809DA5EF65ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4649A450-41CD-4CD9-8E00-E0ED4DCA52DB}"/>
+  <xr:revisionPtr revIDLastSave="246" documentId="11_F25DC773A252ABDACC10485809DA5EF65ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D1D8700-951A-4524-B068-ECF59A5510CA}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="12196" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="86">
   <si>
     <t>Component</t>
   </si>
@@ -204,15 +204,9 @@
     <t>SW1 / 2</t>
   </si>
   <si>
-    <t>1528-2831-ND</t>
-  </si>
-  <si>
     <t>Adafruit Industries LLC</t>
   </si>
   <si>
-    <t>2X20 SOCKET RISER HEADER FOR RPI</t>
-  </si>
-  <si>
     <t>MCP2515</t>
   </si>
   <si>
@@ -277,6 +271,18 @@
   </si>
   <si>
     <t>TSR 3-2450N</t>
+  </si>
+  <si>
+    <t>1528-1385-ND</t>
+  </si>
+  <si>
+    <t>STACKING HEADER 40PIN</t>
+  </si>
+  <si>
+    <t>Standoffs</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/w%C3%BCrth-elektronik/971110155/9488763?__cf_chl_rt_tk=xcFdo20YsRVDmn6iAvWDZHgvISnmkhCO.rw0HPXhjNg-1792913777-1.0.1.1-JwCE.SXpXSUpdrF4BQAAZtpdkCJjS.Sfn0_rh3RrmUc</t>
   </si>
 </sst>
 </file>
@@ -654,7 +660,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:L22"/>
+  <dimension ref="A2:L21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="14.19921875" customWidth="1"/>
@@ -725,7 +731,7 @@
         <v>25</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>26</v>
@@ -737,7 +743,7 @@
         <v>10</v>
       </c>
       <c r="K4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L4" t="s">
         <v>23</v>
@@ -770,7 +776,7 @@
         <v>7</v>
       </c>
       <c r="K5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.45">
@@ -778,10 +784,10 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>15</v>
@@ -802,7 +808,7 @@
         <v>7</v>
       </c>
       <c r="K6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.45">
@@ -926,10 +932,10 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I12">
         <v>4</v>
@@ -940,15 +946,67 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I13">
         <v>2</v>
       </c>
       <c r="J13" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="B14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" t="s">
+        <v>63</v>
+      </c>
+      <c r="H14" t="s">
+        <v>64</v>
+      </c>
+      <c r="I14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="B15" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15" t="s">
+        <v>67</v>
+      </c>
+      <c r="F15" t="s">
+        <v>68</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H15" t="s">
+        <v>69</v>
+      </c>
+      <c r="I15">
+        <v>2</v>
+      </c>
+      <c r="J15" s="4" t="s">
         <v>7</v>
       </c>
     </row>
@@ -960,19 +1018,19 @@
         <v>57</v>
       </c>
       <c r="C20" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D20">
-        <v>4079</v>
+        <v>2223</v>
       </c>
       <c r="E20" t="s">
+        <v>82</v>
+      </c>
+      <c r="F20" t="s">
         <v>59</v>
       </c>
-      <c r="F20" t="s">
-        <v>60</v>
-      </c>
       <c r="H20" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="I20">
         <v>2</v>
@@ -983,54 +1041,13 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21" t="s">
-        <v>75</v>
-      </c>
-      <c r="D21" t="s">
-        <v>64</v>
-      </c>
-      <c r="E21" t="s">
-        <v>63</v>
-      </c>
-      <c r="F21" t="s">
-        <v>65</v>
-      </c>
-      <c r="H21" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="I21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="B22" t="s">
-        <v>67</v>
-      </c>
-      <c r="C22" t="s">
-        <v>68</v>
-      </c>
-      <c r="D22" t="s">
-        <v>73</v>
-      </c>
-      <c r="E22" t="s">
-        <v>69</v>
-      </c>
-      <c r="F22" t="s">
-        <v>70</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="H22" t="s">
-        <v>71</v>
-      </c>
-      <c r="I22">
-        <v>2</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="J21" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -1044,10 +1061,10 @@
     <hyperlink ref="J9" r:id="rId7" xr:uid="{798877DA-B291-4CC0-84A7-001B9134CF0B}"/>
     <hyperlink ref="J10" r:id="rId8" xr:uid="{00E66CDD-5400-4FE1-89A5-0B9266D05039}"/>
     <hyperlink ref="J11" r:id="rId9" xr:uid="{9BE63AE3-6695-42BA-8E8F-2E98D962A63D}"/>
-    <hyperlink ref="J20" r:id="rId10" xr:uid="{E0D90F7C-094F-47C4-9689-4F38ABBDE890}"/>
-    <hyperlink ref="J22" r:id="rId11" xr:uid="{CEE19911-DD7A-45AF-839A-7B0BEFDAB83D}"/>
-    <hyperlink ref="J12" r:id="rId12" xr:uid="{47204ACE-9606-4881-B595-BDDC0AF532F3}"/>
-    <hyperlink ref="J13" r:id="rId13" xr:uid="{930E413D-5037-4B2D-90BF-4D2E6AEE824F}"/>
+    <hyperlink ref="J15" r:id="rId10" xr:uid="{CEE19911-DD7A-45AF-839A-7B0BEFDAB83D}"/>
+    <hyperlink ref="J12" r:id="rId11" xr:uid="{47204ACE-9606-4881-B595-BDDC0AF532F3}"/>
+    <hyperlink ref="J13" r:id="rId12" xr:uid="{930E413D-5037-4B2D-90BF-4D2E6AEE824F}"/>
+    <hyperlink ref="J20" r:id="rId13" xr:uid="{E0D90F7C-094F-47C4-9689-4F38ABBDE890}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId14"/>

--- a/Components.xlsx
+++ b/Components.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nuwildcat-my.sharepoint.com/personal/org0708_ads_northwestern_edu/Documents/Northwestern/Extracurricular/hardware/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="246" documentId="11_F25DC773A252ABDACC10485809DA5EF65ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D1D8700-951A-4524-B068-ECF59A5510CA}"/>
+  <xr:revisionPtr revIDLastSave="262" documentId="11_F25DC773A252ABDACC10485809DA5EF65ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31717A1D-A2B5-48A9-9B69-A6827516B842}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="12196" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="81">
   <si>
     <t>Component</t>
   </si>
@@ -144,21 +144,6 @@
     <t>TVS</t>
   </si>
   <si>
-    <t>1727-3891-2-ND</t>
-  </si>
-  <si>
-    <t>Nexperia USA Inc.</t>
-  </si>
-  <si>
-    <t>PESD2CAN,215</t>
-  </si>
-  <si>
-    <t>41V Clamp 5A (8/20µs) Ipp Tvs Diode Surface Mount TO-236AB</t>
-  </si>
-  <si>
-    <t>Surface Mount TO-236AB</t>
-  </si>
-  <si>
     <t>CMC</t>
   </si>
   <si>
@@ -228,36 +213,15 @@
     <t>Y1</t>
   </si>
   <si>
-    <t>535-10630-2-ND</t>
-  </si>
-  <si>
     <t>Abracon LLC</t>
   </si>
   <si>
-    <t>CRYSTAL 8.0000MHZ 18PF SMD</t>
-  </si>
-  <si>
-    <t>2-SMD,</t>
-  </si>
-  <si>
-    <t>ABM3-8.000MHZ-D2Y-T</t>
-  </si>
-  <si>
     <t>J1</t>
   </si>
   <si>
     <t>U3</t>
   </si>
   <si>
-    <t>22pF Cap (crystal)</t>
-  </si>
-  <si>
-    <t>Resistor</t>
-  </si>
-  <si>
-    <t>R4</t>
-  </si>
-  <si>
     <t>C10 / C11</t>
   </si>
   <si>
@@ -283,6 +247,27 @@
   </si>
   <si>
     <t>https://www.digikey.com/en/products/detail/w%C3%BCrth-elektronik/971110155/9488763?__cf_chl_rt_tk=xcFdo20YsRVDmn6iAvWDZHgvISnmkhCO.rw0HPXhjNg-1792913777-1.0.1.1-JwCE.SXpXSUpdrF4BQAAZtpdkCJjS.Sfn0_rh3RrmUc</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/microchip-technology/MCP2515-I-SO/593001</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/abracon-llc/ABM3-16-000MHZ-D2Y-T/2344578</t>
+  </si>
+  <si>
+    <t>Diode</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/onsemi/1N4148/458603</t>
+  </si>
+  <si>
+    <t>16MHz</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/nexperia-usa-inc/PESD2CANFD24VT-QR/16681632</t>
   </si>
 </sst>
 </file>
@@ -660,7 +645,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:L21"/>
+  <dimension ref="A2:L20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="14.19921875" customWidth="1"/>
@@ -731,7 +716,7 @@
         <v>25</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>26</v>
@@ -743,7 +728,7 @@
         <v>10</v>
       </c>
       <c r="K4" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="L4" t="s">
         <v>23</v>
@@ -776,7 +761,7 @@
         <v>7</v>
       </c>
       <c r="K5" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.45">
@@ -784,10 +769,10 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D6" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>15</v>
@@ -808,7 +793,7 @@
         <v>7</v>
       </c>
       <c r="K6" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.45">
@@ -851,51 +836,37 @@
         <v>38</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" t="s">
         <v>40</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H9" t="s">
-        <v>42</v>
-      </c>
+      <c r="G9" s="3"/>
       <c r="I9">
         <v>2</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" t="s">
         <v>44</v>
-      </c>
-      <c r="C10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" t="s">
-        <v>48</v>
-      </c>
-      <c r="F10" t="s">
-        <v>49</v>
       </c>
       <c r="G10" t="s">
         <v>36</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I10">
         <v>2</v>
@@ -906,22 +877,22 @@
     </row>
     <row r="11" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F11" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="I11">
         <v>4</v>
@@ -931,11 +902,8 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B12" t="s">
-        <v>74</v>
-      </c>
       <c r="C12" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="I12">
         <v>4</v>
@@ -946,16 +914,28 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="C13" t="s">
-        <v>76</v>
+        <v>64</v>
+      </c>
+      <c r="D13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" t="s">
+        <v>56</v>
+      </c>
+      <c r="F13" t="s">
+        <v>58</v>
+      </c>
+      <c r="H13" t="s">
+        <v>59</v>
       </c>
       <c r="I13">
         <v>2</v>
       </c>
-      <c r="J13" s="4" t="s">
-        <v>7</v>
+      <c r="J13" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.45">
@@ -963,91 +943,74 @@
         <v>60</v>
       </c>
       <c r="C14" t="s">
-        <v>73</v>
-      </c>
-      <c r="D14" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" t="s">
         <v>62</v>
       </c>
-      <c r="E14" t="s">
-        <v>61</v>
-      </c>
-      <c r="F14" t="s">
-        <v>63</v>
-      </c>
+      <c r="G14" s="3"/>
       <c r="H14" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="I14">
         <v>2</v>
       </c>
+      <c r="J14" s="4" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>66</v>
-      </c>
-      <c r="D15" t="s">
-        <v>71</v>
-      </c>
-      <c r="E15" t="s">
-        <v>67</v>
-      </c>
-      <c r="F15" t="s">
-        <v>68</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="H15" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="I15">
         <v>2</v>
       </c>
-      <c r="J15" s="4" t="s">
+      <c r="J15" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A19" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19">
+        <v>2223</v>
+      </c>
+      <c r="E19" t="s">
+        <v>70</v>
+      </c>
+      <c r="F19" t="s">
+        <v>54</v>
+      </c>
+      <c r="H19" t="s">
+        <v>71</v>
+      </c>
+      <c r="I19">
+        <v>2</v>
+      </c>
+      <c r="J19" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A20" s="6" t="s">
-        <v>56</v>
-      </c>
       <c r="B20" t="s">
-        <v>57</v>
-      </c>
-      <c r="C20" t="s">
         <v>72</v>
       </c>
-      <c r="D20">
-        <v>2223</v>
-      </c>
-      <c r="E20" t="s">
-        <v>82</v>
-      </c>
-      <c r="F20" t="s">
-        <v>59</v>
-      </c>
-      <c r="H20" t="s">
-        <v>83</v>
-      </c>
       <c r="I20">
-        <v>2</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="B21" t="s">
-        <v>84</v>
-      </c>
-      <c r="I21">
         <v>8</v>
       </c>
-      <c r="J21" t="s">
-        <v>85</v>
+      <c r="J20" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1058,15 +1021,12 @@
     <hyperlink ref="J5" r:id="rId4" xr:uid="{BB308056-6C69-4446-ABC1-0CEE27EE8208}"/>
     <hyperlink ref="F4" r:id="rId5" display="https://www.digikey.com/en/supplier-centers/alpha-and-omega-semiconductor" xr:uid="{B79ECA54-82EC-40BB-888A-002F6800B9B3}"/>
     <hyperlink ref="J8" r:id="rId6" xr:uid="{11F395D0-5504-489D-8656-EE1A54C23DDA}"/>
-    <hyperlink ref="J9" r:id="rId7" xr:uid="{798877DA-B291-4CC0-84A7-001B9134CF0B}"/>
-    <hyperlink ref="J10" r:id="rId8" xr:uid="{00E66CDD-5400-4FE1-89A5-0B9266D05039}"/>
-    <hyperlink ref="J11" r:id="rId9" xr:uid="{9BE63AE3-6695-42BA-8E8F-2E98D962A63D}"/>
-    <hyperlink ref="J15" r:id="rId10" xr:uid="{CEE19911-DD7A-45AF-839A-7B0BEFDAB83D}"/>
-    <hyperlink ref="J12" r:id="rId11" xr:uid="{47204ACE-9606-4881-B595-BDDC0AF532F3}"/>
-    <hyperlink ref="J13" r:id="rId12" xr:uid="{930E413D-5037-4B2D-90BF-4D2E6AEE824F}"/>
-    <hyperlink ref="J20" r:id="rId13" xr:uid="{E0D90F7C-094F-47C4-9689-4F38ABBDE890}"/>
+    <hyperlink ref="J10" r:id="rId7" xr:uid="{00E66CDD-5400-4FE1-89A5-0B9266D05039}"/>
+    <hyperlink ref="J11" r:id="rId8" xr:uid="{9BE63AE3-6695-42BA-8E8F-2E98D962A63D}"/>
+    <hyperlink ref="J12" r:id="rId9" xr:uid="{47204ACE-9606-4881-B595-BDDC0AF532F3}"/>
+    <hyperlink ref="J19" r:id="rId10" xr:uid="{E0D90F7C-094F-47C4-9689-4F38ABBDE890}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId14"/>
+  <pageSetup orientation="portrait" r:id="rId11"/>
 </worksheet>
 </file>
--- a/Components.xlsx
+++ b/Components.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nuwildcat-my.sharepoint.com/personal/org0708_ads_northwestern_edu/Documents/Northwestern/Extracurricular/hardware/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="262" documentId="11_F25DC773A252ABDACC10485809DA5EF65ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31717A1D-A2B5-48A9-9B69-A6827516B842}"/>
+  <xr:revisionPtr revIDLastSave="324" documentId="11_F25DC773A252ABDACC10485809DA5EF65ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B19D78D-2F96-4783-8BCD-3DA84C76B489}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="12196" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="99">
   <si>
     <t>Component</t>
   </si>
@@ -144,6 +144,9 @@
     <t>TVS</t>
   </si>
   <si>
+    <t>Nexperia USA Inc.</t>
+  </si>
+  <si>
     <t>CMC</t>
   </si>
   <si>
@@ -222,9 +225,6 @@
     <t>U3</t>
   </si>
   <si>
-    <t>C10 / C11</t>
-  </si>
-  <si>
     <t>Package_TO_SOT_SMD:TO-252-2</t>
   </si>
   <si>
@@ -249,32 +249,86 @@
     <t>https://www.digikey.com/en/products/detail/w%C3%BCrth-elektronik/971110155/9488763?__cf_chl_rt_tk=xcFdo20YsRVDmn6iAvWDZHgvISnmkhCO.rw0HPXhjNg-1792913777-1.0.1.1-JwCE.SXpXSUpdrF4BQAAZtpdkCJjS.Sfn0_rh3RrmUc</t>
   </si>
   <si>
-    <t>https://www.digikey.com/en/products/detail/microchip-technology/MCP2515-I-SO/593001</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/abracon-llc/ABM3-16-000MHZ-D2Y-T/2344578</t>
-  </si>
-  <si>
     <t>Diode</t>
   </si>
   <si>
     <t>D1</t>
   </si>
   <si>
-    <t>https://www.digikey.com/en/products/detail/onsemi/1N4148/458603</t>
-  </si>
-  <si>
     <t>16MHz</t>
   </si>
   <si>
-    <t>https://www.digikey.com/en/products/detail/nexperia-usa-inc/PESD2CANFD24VT-QR/16681632</t>
+    <t>1727-PESD2CANFD24VT-QRCT-ND</t>
+  </si>
+  <si>
+    <t>Package_TO_SOT_SMD:SOT-23-3</t>
+  </si>
+  <si>
+    <t>TVS DIODE 24VWM 42VC TO236AB</t>
+  </si>
+  <si>
+    <t>PESD2CANFD24VT-QR</t>
+  </si>
+  <si>
+    <t>18-SOIC</t>
+  </si>
+  <si>
+    <t>535-10638-1-ND</t>
+  </si>
+  <si>
+    <t>ABM3-16.000MHZ-D2Y-T</t>
+  </si>
+  <si>
+    <t>1N4148FS-ND</t>
+  </si>
+  <si>
+    <t>onsemi</t>
+  </si>
+  <si>
+    <t>1N4148</t>
+  </si>
+  <si>
+    <t>Diode 100 V 200mA Through Hole DO-35</t>
+  </si>
+  <si>
+    <t>Crystal Caps</t>
+  </si>
+  <si>
+    <t>CAN Caps</t>
+  </si>
+  <si>
+    <t>C19 / C20</t>
+  </si>
+  <si>
+    <t>311-3894-1-ND</t>
+  </si>
+  <si>
+    <t>YAGEO</t>
+  </si>
+  <si>
+    <t>CC0603FRNPO9BN300</t>
+  </si>
+  <si>
+    <t>CAP CER 30PF 50V C0G/NPO 0603</t>
+  </si>
+  <si>
+    <t>C1 / C2</t>
+  </si>
+  <si>
+    <t>Backup crystal caps</t>
+  </si>
+  <si>
+    <t>27pF and 33 pF</t>
+  </si>
+  <si>
+    <t>33pF</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -317,6 +371,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF444444"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -345,7 +405,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -364,6 +424,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -645,7 +706,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:L20"/>
+  <dimension ref="A2:L21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="14.19921875" customWidth="1"/>
@@ -830,43 +891,63 @@
       <c r="J8" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="K8" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>38</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9" s="3"/>
+        <v>41</v>
+      </c>
+      <c r="D9" t="s">
+        <v>80</v>
+      </c>
+      <c r="E9" t="s">
+        <v>77</v>
+      </c>
+      <c r="F9" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H9" t="s">
+        <v>79</v>
+      </c>
       <c r="I9">
         <v>2</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>80</v>
+        <v>7</v>
+      </c>
+      <c r="K9" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G10" t="s">
         <v>36</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I10">
         <v>2</v>
@@ -874,25 +955,28 @@
       <c r="J10" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="K10" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="11" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" t="s">
         <v>49</v>
       </c>
-      <c r="E11" t="s">
-        <v>47</v>
-      </c>
-      <c r="F11" t="s">
-        <v>48</v>
-      </c>
       <c r="H11" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I11">
         <v>4</v>
@@ -900,116 +984,197 @@
       <c r="J11" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="K11" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="C12" t="s">
+      <c r="J12" s="4"/>
+    </row>
+    <row r="13" spans="1:12" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="B13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" t="s">
         <v>65</v>
       </c>
-      <c r="I12">
-        <v>4</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B13" t="s">
-        <v>55</v>
-      </c>
-      <c r="C13" t="s">
-        <v>64</v>
-      </c>
       <c r="D13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" t="s">
         <v>57</v>
       </c>
-      <c r="E13" t="s">
-        <v>56</v>
-      </c>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>81</v>
       </c>
       <c r="H13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I13">
         <v>2</v>
       </c>
-      <c r="J13" t="s">
-        <v>74</v>
+      <c r="J13" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K13" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C14" t="s">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="D14" t="s">
+        <v>83</v>
+      </c>
+      <c r="E14" t="s">
+        <v>82</v>
       </c>
       <c r="F14" t="s">
-        <v>62</v>
-      </c>
-      <c r="G14" s="3"/>
+        <v>63</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="H14" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I14">
         <v>2</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>75</v>
+        <v>7</v>
+      </c>
+      <c r="K14" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>77</v>
+        <v>75</v>
+      </c>
+      <c r="D15" t="s">
+        <v>86</v>
+      </c>
+      <c r="E15" t="s">
+        <v>84</v>
+      </c>
+      <c r="F15" t="s">
+        <v>85</v>
+      </c>
+      <c r="H15" t="s">
+        <v>87</v>
       </c>
       <c r="I15">
         <v>2</v>
       </c>
-      <c r="J15" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A19" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="J15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K15" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="B16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D16" t="s">
+        <v>93</v>
+      </c>
+      <c r="E16" t="s">
+        <v>91</v>
+      </c>
+      <c r="F16" t="s">
+        <v>92</v>
+      </c>
+      <c r="G16">
+        <v>603</v>
+      </c>
+      <c r="H16" t="s">
+        <v>94</v>
+      </c>
+      <c r="I16">
+        <v>4</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="B17" t="s">
+        <v>96</v>
+      </c>
+      <c r="H17" t="s">
+        <v>97</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="B18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" t="s">
+        <v>90</v>
+      </c>
+      <c r="I18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A20" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C19" t="s">
-        <v>63</v>
-      </c>
-      <c r="D19">
+      <c r="B20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20">
         <v>2223</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E20" t="s">
         <v>70</v>
       </c>
-      <c r="F19" t="s">
-        <v>54</v>
-      </c>
-      <c r="H19" t="s">
+      <c r="F20" t="s">
+        <v>55</v>
+      </c>
+      <c r="H20" t="s">
         <v>71</v>
       </c>
-      <c r="I19">
+      <c r="I20">
         <v>2</v>
       </c>
-      <c r="J19" s="4" t="s">
+      <c r="J20" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="B20" t="s">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="B21" t="s">
         <v>72</v>
       </c>
-      <c r="I20">
+      <c r="I21">
         <v>8</v>
       </c>
-      <c r="J20" t="s">
+      <c r="J21" t="s">
         <v>73</v>
       </c>
     </row>
@@ -1023,10 +1188,15 @@
     <hyperlink ref="J8" r:id="rId6" xr:uid="{11F395D0-5504-489D-8656-EE1A54C23DDA}"/>
     <hyperlink ref="J10" r:id="rId7" xr:uid="{00E66CDD-5400-4FE1-89A5-0B9266D05039}"/>
     <hyperlink ref="J11" r:id="rId8" xr:uid="{9BE63AE3-6695-42BA-8E8F-2E98D962A63D}"/>
-    <hyperlink ref="J12" r:id="rId9" xr:uid="{47204ACE-9606-4881-B595-BDDC0AF532F3}"/>
-    <hyperlink ref="J19" r:id="rId10" xr:uid="{E0D90F7C-094F-47C4-9689-4F38ABBDE890}"/>
+    <hyperlink ref="J20" r:id="rId9" xr:uid="{E0D90F7C-094F-47C4-9689-4F38ABBDE890}"/>
+    <hyperlink ref="J9" r:id="rId10" xr:uid="{DE42A9A5-39BC-4817-B668-4848AF823537}"/>
+    <hyperlink ref="J13" r:id="rId11" xr:uid="{6CD35D92-F3FD-492E-917B-74821F76AA6E}"/>
+    <hyperlink ref="J14" r:id="rId12" xr:uid="{5D0CD5F4-CF09-4B0B-9EF4-A72BAD63B893}"/>
+    <hyperlink ref="J15" r:id="rId13" xr:uid="{9FFA7A70-825A-4AE7-AA84-83662A62C65C}"/>
+    <hyperlink ref="J16" r:id="rId14" xr:uid="{C6EE7D64-B7D3-498D-8A0C-182E49FF9909}"/>
+    <hyperlink ref="J17" r:id="rId15" xr:uid="{CA602DEC-6055-4FEF-B8CF-5C4E7CA097D8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId11"/>
+  <pageSetup orientation="portrait" r:id="rId16"/>
 </worksheet>
 </file>
--- a/Components.xlsx
+++ b/Components.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nuwildcat-my.sharepoint.com/personal/org0708_ads_northwestern_edu/Documents/Northwestern/Extracurricular/hardware/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="324" documentId="11_F25DC773A252ABDACC10485809DA5EF65ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B19D78D-2F96-4783-8BCD-3DA84C76B489}"/>
+  <xr:revisionPtr revIDLastSave="332" documentId="11_F25DC773A252ABDACC10485809DA5EF65ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8F3D5CA-82F9-467E-9AA5-AC8DB0136354}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="12196" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="102">
   <si>
     <t>Component</t>
   </si>
@@ -99,6 +99,9 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
+    <t>U2</t>
+  </si>
+  <si>
     <t>785-1833-1-ND</t>
   </si>
   <si>
@@ -322,6 +325,12 @@
   </si>
   <si>
     <t>33pF</t>
+  </si>
+  <si>
+    <t>27pF</t>
+  </si>
+  <si>
+    <t>ADC</t>
   </si>
 </sst>
 </file>
@@ -706,7 +715,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:L21"/>
+  <dimension ref="A2:L25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="14.19921875" customWidth="1"/>
@@ -727,7 +736,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
         <v>2</v>
@@ -768,19 +777,19 @@
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I4">
         <v>2</v>
@@ -789,7 +798,7 @@
         <v>10</v>
       </c>
       <c r="K4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L4" t="s">
         <v>23</v>
@@ -800,7 +809,7 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="3" t="s">
@@ -822,7 +831,7 @@
         <v>7</v>
       </c>
       <c r="K5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.45">
@@ -830,10 +839,10 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>15</v>
@@ -854,7 +863,7 @@
         <v>7</v>
       </c>
       <c r="K6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.45">
@@ -862,28 +871,28 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I8">
         <v>2</v>
@@ -892,30 +901,30 @@
         <v>7</v>
       </c>
       <c r="K8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
+        <v>81</v>
+      </c>
+      <c r="E9" t="s">
+        <v>78</v>
+      </c>
+      <c r="F9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="H9" t="s">
         <v>80</v>
-      </c>
-      <c r="E9" t="s">
-        <v>77</v>
-      </c>
-      <c r="F9" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H9" t="s">
-        <v>79</v>
       </c>
       <c r="I9">
         <v>2</v>
@@ -924,30 +933,30 @@
         <v>7</v>
       </c>
       <c r="K9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I10">
         <v>2</v>
@@ -956,27 +965,27 @@
         <v>7</v>
       </c>
       <c r="K10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" t="s">
         <v>50</v>
       </c>
-      <c r="E11" t="s">
-        <v>48</v>
-      </c>
-      <c r="F11" t="s">
-        <v>49</v>
-      </c>
       <c r="H11" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I11">
         <v>4</v>
@@ -985,7 +994,7 @@
         <v>7</v>
       </c>
       <c r="K11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.45">
@@ -993,25 +1002,25 @@
     </row>
     <row r="13" spans="1:12" ht="15.4" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" t="s">
         <v>58</v>
       </c>
-      <c r="E13" t="s">
-        <v>57</v>
-      </c>
       <c r="F13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I13">
         <v>2</v>
@@ -1020,30 +1029,30 @@
         <v>7</v>
       </c>
       <c r="K13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s">
+        <v>84</v>
+      </c>
+      <c r="E14" t="s">
         <v>83</v>
       </c>
-      <c r="E14" t="s">
-        <v>82</v>
-      </c>
       <c r="F14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H14" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I14">
         <v>2</v>
@@ -1052,27 +1061,27 @@
         <v>7</v>
       </c>
       <c r="K14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D15" t="s">
+        <v>87</v>
+      </c>
+      <c r="E15" t="s">
+        <v>85</v>
+      </c>
+      <c r="F15" t="s">
         <v>86</v>
       </c>
-      <c r="E15" t="s">
-        <v>84</v>
-      </c>
-      <c r="F15" t="s">
-        <v>85</v>
-      </c>
       <c r="H15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I15">
         <v>2</v>
@@ -1081,30 +1090,30 @@
         <v>7</v>
       </c>
       <c r="K15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E16" t="s">
+        <v>92</v>
+      </c>
+      <c r="F16" t="s">
         <v>93</v>
-      </c>
-      <c r="E16" t="s">
-        <v>91</v>
-      </c>
-      <c r="F16" t="s">
-        <v>92</v>
       </c>
       <c r="G16">
         <v>603</v>
       </c>
       <c r="H16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I16">
         <v>4</v>
@@ -1113,69 +1122,89 @@
         <v>7</v>
       </c>
       <c r="K16" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
+        <v>99</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="L17" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I18">
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A20" s="6" t="s">
-        <v>52</v>
+        <v>101</v>
       </c>
       <c r="B20" t="s">
-        <v>53</v>
+        <v>101</v>
       </c>
       <c r="C20" t="s">
-        <v>64</v>
-      </c>
-      <c r="D20">
-        <v>2223</v>
-      </c>
-      <c r="E20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F20" t="s">
-        <v>55</v>
-      </c>
-      <c r="H20" t="s">
-        <v>71</v>
-      </c>
-      <c r="I20">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="B21" t="s">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A24" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" t="s">
+        <v>65</v>
+      </c>
+      <c r="D24">
+        <v>2223</v>
+      </c>
+      <c r="E24" t="s">
+        <v>71</v>
+      </c>
+      <c r="F24" t="s">
+        <v>56</v>
+      </c>
+      <c r="H24" t="s">
         <v>72</v>
       </c>
-      <c r="I21">
+      <c r="I24">
+        <v>2</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="B25" t="s">
+        <v>73</v>
+      </c>
+      <c r="I25">
         <v>8</v>
       </c>
-      <c r="J21" t="s">
-        <v>73</v>
+      <c r="J25" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1188,15 +1217,17 @@
     <hyperlink ref="J8" r:id="rId6" xr:uid="{11F395D0-5504-489D-8656-EE1A54C23DDA}"/>
     <hyperlink ref="J10" r:id="rId7" xr:uid="{00E66CDD-5400-4FE1-89A5-0B9266D05039}"/>
     <hyperlink ref="J11" r:id="rId8" xr:uid="{9BE63AE3-6695-42BA-8E8F-2E98D962A63D}"/>
-    <hyperlink ref="J20" r:id="rId9" xr:uid="{E0D90F7C-094F-47C4-9689-4F38ABBDE890}"/>
+    <hyperlink ref="J24" r:id="rId9" xr:uid="{E0D90F7C-094F-47C4-9689-4F38ABBDE890}"/>
     <hyperlink ref="J9" r:id="rId10" xr:uid="{DE42A9A5-39BC-4817-B668-4848AF823537}"/>
     <hyperlink ref="J13" r:id="rId11" xr:uid="{6CD35D92-F3FD-492E-917B-74821F76AA6E}"/>
     <hyperlink ref="J14" r:id="rId12" xr:uid="{5D0CD5F4-CF09-4B0B-9EF4-A72BAD63B893}"/>
     <hyperlink ref="J15" r:id="rId13" xr:uid="{9FFA7A70-825A-4AE7-AA84-83662A62C65C}"/>
     <hyperlink ref="J16" r:id="rId14" xr:uid="{C6EE7D64-B7D3-498D-8A0C-182E49FF9909}"/>
     <hyperlink ref="J17" r:id="rId15" xr:uid="{CA602DEC-6055-4FEF-B8CF-5C4E7CA097D8}"/>
+    <hyperlink ref="K17" r:id="rId16" xr:uid="{0DA2FBD3-91BB-42D2-86F2-26BC53ADEF37}"/>
+    <hyperlink ref="J20" r:id="rId17" xr:uid="{5ECE52DB-8AB3-4E55-AAFC-EE48888ABB4E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId16"/>
+  <pageSetup orientation="portrait" r:id="rId18"/>
 </worksheet>
 </file>
--- a/Components.xlsx
+++ b/Components.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nuwildcat-my.sharepoint.com/personal/org0708_ads_northwestern_edu/Documents/Northwestern/Extracurricular/hardware/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="332" documentId="11_F25DC773A252ABDACC10485809DA5EF65ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8F3D5CA-82F9-467E-9AA5-AC8DB0136354}"/>
+  <xr:revisionPtr revIDLastSave="381" documentId="11_F25DC773A252ABDACC10485809DA5EF65ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F08DDE97-2318-41B6-A5C7-63238C99AD5E}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="12196" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="124">
   <si>
     <t>Component</t>
   </si>
@@ -249,9 +249,6 @@
     <t>Standoffs</t>
   </si>
   <si>
-    <t>https://www.digikey.com/en/products/detail/w%C3%BCrth-elektronik/971110155/9488763?__cf_chl_rt_tk=xcFdo20YsRVDmn6iAvWDZHgvISnmkhCO.rw0HPXhjNg-1792913777-1.0.1.1-JwCE.SXpXSUpdrF4BQAAZtpdkCJjS.Sfn0_rh3RrmUc</t>
-  </si>
-  <si>
     <t>Diode</t>
   </si>
   <si>
@@ -300,9 +297,6 @@
     <t>CAN Caps</t>
   </si>
   <si>
-    <t>C19 / C20</t>
-  </si>
-  <si>
     <t>311-3894-1-ND</t>
   </si>
   <si>
@@ -331,6 +325,78 @@
   </si>
   <si>
     <t>ADC</t>
+  </si>
+  <si>
+    <t>296-45221-1-ND</t>
+  </si>
+  <si>
+    <t>Texas Instruments</t>
+  </si>
+  <si>
+    <t>ADS1115BQDGSRQ1</t>
+  </si>
+  <si>
+    <t>16 Bit Analog to Digital Converter 2, 4 Input 1 Sigma-Delta 10-VSSOP</t>
+  </si>
+  <si>
+    <t>custom</t>
+  </si>
+  <si>
+    <t>Decoupling / Bypass</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>399-6853-1-ND</t>
+  </si>
+  <si>
+    <t>KEMET</t>
+  </si>
+  <si>
+    <t>C0603C104J5RACAUTO</t>
+  </si>
+  <si>
+    <t>0603_Hand_Solder</t>
+  </si>
+  <si>
+    <t>0.1 µF ±5% 50V Ceramic Capacitor X7R 0603 (1608 Metric)</t>
+  </si>
+  <si>
+    <t>399-C0805C475J3RACAUTOCT-ND</t>
+  </si>
+  <si>
+    <t>C0805C475J3RACAUTO</t>
+  </si>
+  <si>
+    <t>CAP CER 4.7UF 25V X7R 0805</t>
+  </si>
+  <si>
+    <t>General</t>
+  </si>
+  <si>
+    <t>C16/C17</t>
+  </si>
+  <si>
+    <t>399-17584-1-ND</t>
+  </si>
+  <si>
+    <t>CAP CER 220PF 50V X7R 0603</t>
+  </si>
+  <si>
+    <t>C0603C221J5RACAUTO</t>
+  </si>
+  <si>
+    <t>732-13059-ND</t>
+  </si>
+  <si>
+    <t>Würth Elektronik</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>HEX STANDOFF M2.5 POLYAMIDE 11MM</t>
   </si>
 </sst>
 </file>
@@ -715,7 +781,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:L25"/>
+  <dimension ref="A2:L29"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="14.19921875" customWidth="1"/>
@@ -912,19 +978,19 @@
         <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F9" t="s">
         <v>40</v>
       </c>
       <c r="G9" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H9" t="s">
         <v>79</v>
-      </c>
-      <c r="H9" t="s">
-        <v>80</v>
       </c>
       <c r="I9">
         <v>2</v>
@@ -997,30 +1063,59 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="J12" s="4"/>
-    </row>
-    <row r="13" spans="1:12" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:12" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="B12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" t="s">
+        <v>58</v>
+      </c>
+      <c r="F12" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="H12" t="s">
+        <v>61</v>
+      </c>
+      <c r="I12">
+        <v>2</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C13" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D13" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="E13" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="F13" t="s">
-        <v>60</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>82</v>
+        <v>64</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="H13" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="I13">
         <v>2</v>
@@ -1034,25 +1129,22 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="D14" t="s">
+        <v>86</v>
+      </c>
+      <c r="E14" t="s">
         <v>84</v>
       </c>
-      <c r="E14" t="s">
-        <v>83</v>
-      </c>
       <c r="F14" t="s">
-        <v>64</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>37</v>
+        <v>85</v>
       </c>
       <c r="H14" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="I14">
         <v>2</v>
@@ -1066,25 +1158,28 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="D15" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E15" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F15" t="s">
-        <v>86</v>
+        <v>91</v>
+      </c>
+      <c r="G15">
+        <v>603</v>
       </c>
       <c r="H15" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="I15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>7</v>
@@ -1095,79 +1190,86 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
+        <v>95</v>
+      </c>
+      <c r="H16" t="s">
+        <v>96</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L16" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="B17" t="s">
         <v>89</v>
       </c>
-      <c r="C16" t="s">
-        <v>96</v>
-      </c>
-      <c r="D16" t="s">
-        <v>94</v>
-      </c>
-      <c r="E16" t="s">
-        <v>92</v>
-      </c>
-      <c r="F16" t="s">
-        <v>93</v>
-      </c>
-      <c r="G16">
+      <c r="C17" t="s">
+        <v>116</v>
+      </c>
+      <c r="D17" t="s">
+        <v>119</v>
+      </c>
+      <c r="E17" t="s">
+        <v>117</v>
+      </c>
+      <c r="F17" t="s">
+        <v>108</v>
+      </c>
+      <c r="G17">
         <v>603</v>
       </c>
-      <c r="H16" t="s">
-        <v>95</v>
-      </c>
-      <c r="I16">
+      <c r="H17" t="s">
+        <v>118</v>
+      </c>
+      <c r="I17">
         <v>4</v>
       </c>
-      <c r="J16" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K16" t="s">
+      <c r="J17" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K17" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B17" t="s">
-        <v>97</v>
-      </c>
-      <c r="H17" t="s">
-        <v>98</v>
-      </c>
-      <c r="J17" s="4" t="s">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A20" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="K17" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="L17" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B18" t="s">
-        <v>90</v>
-      </c>
-      <c r="C18" t="s">
-        <v>91</v>
-      </c>
-      <c r="I18">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A20" s="6" t="s">
-        <v>101</v>
-      </c>
       <c r="B20" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C20" t="s">
         <v>24</v>
       </c>
+      <c r="D20" t="s">
+        <v>102</v>
+      </c>
+      <c r="E20" t="s">
+        <v>100</v>
+      </c>
+      <c r="F20" t="s">
+        <v>101</v>
+      </c>
+      <c r="G20" t="s">
+        <v>104</v>
+      </c>
+      <c r="H20" t="s">
+        <v>103</v>
+      </c>
+      <c r="I20">
+        <v>2</v>
+      </c>
       <c r="J20" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A24" s="6" t="s">
         <v>53</v>
       </c>
@@ -1195,16 +1297,95 @@
       <c r="J24" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="K24" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
         <v>73</v>
       </c>
+      <c r="C25" t="s">
+        <v>122</v>
+      </c>
+      <c r="D25">
+        <v>971110155</v>
+      </c>
+      <c r="E25" t="s">
+        <v>120</v>
+      </c>
+      <c r="F25" t="s">
+        <v>121</v>
+      </c>
+      <c r="H25" t="s">
+        <v>123</v>
+      </c>
       <c r="I25">
         <v>8</v>
       </c>
-      <c r="J25" t="s">
-        <v>74</v>
+      <c r="J25" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A28" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B28" t="s">
+        <v>105</v>
+      </c>
+      <c r="C28" t="s">
+        <v>106</v>
+      </c>
+      <c r="D28" t="s">
+        <v>109</v>
+      </c>
+      <c r="E28" t="s">
+        <v>107</v>
+      </c>
+      <c r="F28" t="s">
+        <v>108</v>
+      </c>
+      <c r="G28" t="s">
+        <v>110</v>
+      </c>
+      <c r="H28" t="s">
+        <v>111</v>
+      </c>
+      <c r="I28">
+        <v>10</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="B29" t="s">
+        <v>105</v>
+      </c>
+      <c r="C29" t="s">
+        <v>106</v>
+      </c>
+      <c r="D29" t="s">
+        <v>113</v>
+      </c>
+      <c r="E29" t="s">
+        <v>112</v>
+      </c>
+      <c r="F29" t="s">
+        <v>108</v>
+      </c>
+      <c r="G29">
+        <v>805</v>
+      </c>
+      <c r="H29" t="s">
+        <v>114</v>
+      </c>
+      <c r="I29">
+        <v>3</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1219,15 +1400,19 @@
     <hyperlink ref="J11" r:id="rId8" xr:uid="{9BE63AE3-6695-42BA-8E8F-2E98D962A63D}"/>
     <hyperlink ref="J24" r:id="rId9" xr:uid="{E0D90F7C-094F-47C4-9689-4F38ABBDE890}"/>
     <hyperlink ref="J9" r:id="rId10" xr:uid="{DE42A9A5-39BC-4817-B668-4848AF823537}"/>
-    <hyperlink ref="J13" r:id="rId11" xr:uid="{6CD35D92-F3FD-492E-917B-74821F76AA6E}"/>
-    <hyperlink ref="J14" r:id="rId12" xr:uid="{5D0CD5F4-CF09-4B0B-9EF4-A72BAD63B893}"/>
-    <hyperlink ref="J15" r:id="rId13" xr:uid="{9FFA7A70-825A-4AE7-AA84-83662A62C65C}"/>
-    <hyperlink ref="J16" r:id="rId14" xr:uid="{C6EE7D64-B7D3-498D-8A0C-182E49FF9909}"/>
-    <hyperlink ref="J17" r:id="rId15" xr:uid="{CA602DEC-6055-4FEF-B8CF-5C4E7CA097D8}"/>
-    <hyperlink ref="K17" r:id="rId16" xr:uid="{0DA2FBD3-91BB-42D2-86F2-26BC53ADEF37}"/>
+    <hyperlink ref="J12" r:id="rId11" xr:uid="{6CD35D92-F3FD-492E-917B-74821F76AA6E}"/>
+    <hyperlink ref="J13" r:id="rId12" xr:uid="{5D0CD5F4-CF09-4B0B-9EF4-A72BAD63B893}"/>
+    <hyperlink ref="J14" r:id="rId13" xr:uid="{9FFA7A70-825A-4AE7-AA84-83662A62C65C}"/>
+    <hyperlink ref="J15" r:id="rId14" xr:uid="{C6EE7D64-B7D3-498D-8A0C-182E49FF9909}"/>
+    <hyperlink ref="J16" r:id="rId15" xr:uid="{CA602DEC-6055-4FEF-B8CF-5C4E7CA097D8}"/>
+    <hyperlink ref="K16" r:id="rId16" xr:uid="{0DA2FBD3-91BB-42D2-86F2-26BC53ADEF37}"/>
     <hyperlink ref="J20" r:id="rId17" xr:uid="{5ECE52DB-8AB3-4E55-AAFC-EE48888ABB4E}"/>
+    <hyperlink ref="J28" r:id="rId18" xr:uid="{9B9D0334-4414-41B1-AFC9-C38746C7F6AB}"/>
+    <hyperlink ref="J29" r:id="rId19" xr:uid="{D5042539-9629-4DAD-A5DE-1A0DB1EDA443}"/>
+    <hyperlink ref="J17" r:id="rId20" xr:uid="{5D9BDD0B-66A9-48F4-AB3E-E7DF27C9C69E}"/>
+    <hyperlink ref="J25" r:id="rId21" xr:uid="{6647EFF2-FEDE-4CF5-B940-BC01E6A58DBF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId18"/>
+  <pageSetup orientation="portrait" r:id="rId22"/>
 </worksheet>
 </file>
--- a/Components.xlsx
+++ b/Components.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nuwildcat-my.sharepoint.com/personal/org0708_ads_northwestern_edu/Documents/Northwestern/Extracurricular/hardware/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="381" documentId="11_F25DC773A252ABDACC10485809DA5EF65ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F08DDE97-2318-41B6-A5C7-63238C99AD5E}"/>
+  <xr:revisionPtr revIDLastSave="422" documentId="11_F25DC773A252ABDACC10485809DA5EF65ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83068B3B-37BD-4A00-A6D2-9BFAC2366ABF}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="12196" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="137">
   <si>
     <t>Component</t>
   </si>
@@ -397,6 +397,45 @@
   </si>
   <si>
     <t>HEX STANDOFF M2.5 POLYAMIDE 11MM</t>
+  </si>
+  <si>
+    <t>QUESTION</t>
+  </si>
+  <si>
+    <t>RC0805FR-071KL</t>
+  </si>
+  <si>
+    <t>311-1.00KCRCT-ND</t>
+  </si>
+  <si>
+    <t>RES 1K OHM 1% 1/8W 0805</t>
+  </si>
+  <si>
+    <t>1k Resistor</t>
+  </si>
+  <si>
+    <t>R3 / R4</t>
+  </si>
+  <si>
+    <t>Termination</t>
+  </si>
+  <si>
+    <t>R5 / R6</t>
+  </si>
+  <si>
+    <t>311-60.4HRCT-ND</t>
+  </si>
+  <si>
+    <t>RC0603FR-0760R4L</t>
+  </si>
+  <si>
+    <t>RES 60.4 OHM 1% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>10k pull up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R7 / R1 / R8 </t>
   </si>
 </sst>
 </file>
@@ -781,7 +820,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:L29"/>
+  <dimension ref="A2:L33"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="14.19921875" customWidth="1"/>
@@ -932,65 +971,33 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="D7" s="1"/>
-    </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A8" s="6" t="s">
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A9" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B9" t="s">
         <v>31</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C9" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E9" t="s">
         <v>35</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F9" t="s">
         <v>36</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G9" t="s">
         <v>37</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H9" t="s">
         <v>38</v>
-      </c>
-      <c r="I8">
-        <v>2</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K8" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B9" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E9" t="s">
-        <v>77</v>
-      </c>
-      <c r="F9" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H9" t="s">
-        <v>79</v>
       </c>
       <c r="I9">
         <v>2</v>
@@ -1002,27 +1009,27 @@
         <v>68</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="E10" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="F10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G10" t="s">
-        <v>37</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>47</v>
+        <v>40</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H10" t="s">
+        <v>79</v>
       </c>
       <c r="I10">
         <v>2</v>
@@ -1036,86 +1043,86 @@
     </row>
     <row r="11" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="I11">
+        <v>2</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K11" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="B12" t="s">
         <v>48</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C12" t="s">
         <v>55</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D12" t="s">
         <v>51</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E12" t="s">
         <v>49</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F12" t="s">
         <v>50</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I11">
+      <c r="I12">
         <v>4</v>
       </c>
-      <c r="J11" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K11" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="B12" t="s">
+      <c r="J12" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="15.4" x14ac:dyDescent="0.45">
+      <c r="B13" t="s">
         <v>57</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C13" t="s">
         <v>66</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D13" t="s">
         <v>59</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E13" t="s">
         <v>58</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F13" t="s">
         <v>60</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G13" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H13" t="s">
         <v>61</v>
-      </c>
-      <c r="I12">
-        <v>2</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K12" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B13" t="s">
-        <v>62</v>
-      </c>
-      <c r="C13" t="s">
-        <v>63</v>
-      </c>
-      <c r="D13" t="s">
-        <v>83</v>
-      </c>
-      <c r="E13" t="s">
-        <v>82</v>
-      </c>
-      <c r="F13" t="s">
-        <v>64</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H13" t="s">
-        <v>76</v>
       </c>
       <c r="I13">
         <v>2</v>
@@ -1129,22 +1136,25 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E14" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F14" t="s">
-        <v>85</v>
+        <v>64</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="H14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="I14">
         <v>2</v>
@@ -1158,28 +1168,25 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="D15" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E15" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F15" t="s">
-        <v>91</v>
-      </c>
-      <c r="G15">
-        <v>603</v>
+        <v>85</v>
       </c>
       <c r="H15" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="I15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>7</v>
@@ -1190,202 +1197,324 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" t="s">
+        <v>92</v>
+      </c>
+      <c r="E16" t="s">
+        <v>90</v>
+      </c>
+      <c r="F16" t="s">
+        <v>91</v>
+      </c>
+      <c r="G16">
+        <v>603</v>
+      </c>
+      <c r="H16" t="s">
+        <v>93</v>
+      </c>
+      <c r="I16">
+        <v>4</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K16" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="B17" t="s">
         <v>95</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H17" t="s">
         <v>96</v>
       </c>
-      <c r="J16" s="4" t="s">
+      <c r="J17" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="K16" s="4" t="s">
+      <c r="K17" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="L16" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="B17" t="s">
+      <c r="L17" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="B18" t="s">
         <v>89</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C18" t="s">
         <v>116</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D18" t="s">
         <v>119</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E18" t="s">
         <v>117</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F18" t="s">
         <v>108</v>
       </c>
-      <c r="G17">
+      <c r="G18">
         <v>603</v>
       </c>
-      <c r="H17" t="s">
+      <c r="H18" t="s">
         <v>118</v>
       </c>
-      <c r="I17">
+      <c r="I18">
         <v>4</v>
       </c>
-      <c r="J17" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K17" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A20" s="6" t="s">
+      <c r="J18" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K18" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="B19" t="s">
+        <v>130</v>
+      </c>
+      <c r="C19" t="s">
+        <v>131</v>
+      </c>
+      <c r="D19" t="s">
+        <v>133</v>
+      </c>
+      <c r="E19" t="s">
+        <v>132</v>
+      </c>
+      <c r="F19" t="s">
+        <v>91</v>
+      </c>
+      <c r="G19">
+        <v>603</v>
+      </c>
+      <c r="H19" t="s">
+        <v>134</v>
+      </c>
+      <c r="I19">
+        <v>12</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K19" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A22" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B22" t="s">
         <v>99</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C22" t="s">
         <v>24</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D22" t="s">
         <v>102</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E22" t="s">
         <v>100</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F22" t="s">
         <v>101</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G22" t="s">
         <v>104</v>
       </c>
-      <c r="H20" t="s">
+      <c r="H22" t="s">
         <v>103</v>
       </c>
-      <c r="I20">
+      <c r="I22">
         <v>2</v>
       </c>
-      <c r="J20" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A24" s="6" t="s">
+      <c r="J22" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K22" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A26" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B26" t="s">
         <v>54</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C26" t="s">
         <v>65</v>
       </c>
-      <c r="D24">
+      <c r="D26">
         <v>2223</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E26" t="s">
         <v>71</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F26" t="s">
         <v>56</v>
       </c>
-      <c r="H24" t="s">
+      <c r="H26" t="s">
         <v>72</v>
       </c>
-      <c r="I24">
+      <c r="I26">
         <v>2</v>
       </c>
-      <c r="J24" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K24" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="B25" t="s">
+      <c r="J26" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K26" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="B27" t="s">
         <v>73</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C27" t="s">
         <v>122</v>
       </c>
-      <c r="D25">
+      <c r="D27">
         <v>971110155</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E27" t="s">
         <v>120</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F27" t="s">
         <v>121</v>
       </c>
-      <c r="H25" t="s">
+      <c r="H27" t="s">
         <v>123</v>
       </c>
-      <c r="I25">
+      <c r="I27">
         <v>8</v>
       </c>
-      <c r="J25" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A28" s="6" t="s">
+      <c r="J27" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K27" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A30" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B30" t="s">
         <v>105</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C30" t="s">
         <v>106</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D30" t="s">
         <v>109</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E30" t="s">
         <v>107</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F30" t="s">
         <v>108</v>
       </c>
-      <c r="G28" t="s">
+      <c r="G30" t="s">
         <v>110</v>
       </c>
-      <c r="H28" t="s">
+      <c r="H30" t="s">
         <v>111</v>
       </c>
-      <c r="I28">
+      <c r="I30">
         <v>10</v>
       </c>
-      <c r="J28" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="B29" t="s">
+      <c r="J30" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K30" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="B31" t="s">
         <v>105</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C31" t="s">
         <v>106</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D31" t="s">
         <v>113</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E31" t="s">
         <v>112</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F31" t="s">
         <v>108</v>
       </c>
-      <c r="G29">
+      <c r="G31">
         <v>805</v>
       </c>
-      <c r="H29" t="s">
+      <c r="H31" t="s">
         <v>114</v>
       </c>
-      <c r="I29">
+      <c r="I31">
         <v>3</v>
       </c>
-      <c r="J29" s="4" t="s">
-        <v>7</v>
+      <c r="J31" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K31" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="B32" t="s">
+        <v>128</v>
+      </c>
+      <c r="C32" t="s">
+        <v>129</v>
+      </c>
+      <c r="D32" t="s">
+        <v>125</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G32" s="3">
+        <v>805</v>
+      </c>
+      <c r="H32" t="s">
+        <v>127</v>
+      </c>
+      <c r="I32">
+        <v>10</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K32" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B33" t="s">
+        <v>135</v>
+      </c>
+      <c r="C33" t="s">
+        <v>136</v>
+      </c>
+      <c r="I33">
+        <v>10</v>
+      </c>
+      <c r="K33" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1395,24 +1524,26 @@
     <hyperlink ref="G5" r:id="rId3" display="https://www.digikey.com/en/products/filter/fuses/1206-3216-metric/139?s=N4IgjCBcpgbFoDGUBmBDANgZwKYBoQA3AOygBcAnAV3xAHsoBtEADgGYB2MCAXQIAcyUEAGVKAS2IBzEAF95QA" xr:uid="{98185761-E669-4D71-BFFE-742816C993DF}"/>
     <hyperlink ref="J5" r:id="rId4" xr:uid="{BB308056-6C69-4446-ABC1-0CEE27EE8208}"/>
     <hyperlink ref="F4" r:id="rId5" display="https://www.digikey.com/en/supplier-centers/alpha-and-omega-semiconductor" xr:uid="{B79ECA54-82EC-40BB-888A-002F6800B9B3}"/>
-    <hyperlink ref="J8" r:id="rId6" xr:uid="{11F395D0-5504-489D-8656-EE1A54C23DDA}"/>
-    <hyperlink ref="J10" r:id="rId7" xr:uid="{00E66CDD-5400-4FE1-89A5-0B9266D05039}"/>
-    <hyperlink ref="J11" r:id="rId8" xr:uid="{9BE63AE3-6695-42BA-8E8F-2E98D962A63D}"/>
-    <hyperlink ref="J24" r:id="rId9" xr:uid="{E0D90F7C-094F-47C4-9689-4F38ABBDE890}"/>
-    <hyperlink ref="J9" r:id="rId10" xr:uid="{DE42A9A5-39BC-4817-B668-4848AF823537}"/>
-    <hyperlink ref="J12" r:id="rId11" xr:uid="{6CD35D92-F3FD-492E-917B-74821F76AA6E}"/>
-    <hyperlink ref="J13" r:id="rId12" xr:uid="{5D0CD5F4-CF09-4B0B-9EF4-A72BAD63B893}"/>
-    <hyperlink ref="J14" r:id="rId13" xr:uid="{9FFA7A70-825A-4AE7-AA84-83662A62C65C}"/>
-    <hyperlink ref="J15" r:id="rId14" xr:uid="{C6EE7D64-B7D3-498D-8A0C-182E49FF9909}"/>
-    <hyperlink ref="J16" r:id="rId15" xr:uid="{CA602DEC-6055-4FEF-B8CF-5C4E7CA097D8}"/>
-    <hyperlink ref="K16" r:id="rId16" xr:uid="{0DA2FBD3-91BB-42D2-86F2-26BC53ADEF37}"/>
-    <hyperlink ref="J20" r:id="rId17" xr:uid="{5ECE52DB-8AB3-4E55-AAFC-EE48888ABB4E}"/>
-    <hyperlink ref="J28" r:id="rId18" xr:uid="{9B9D0334-4414-41B1-AFC9-C38746C7F6AB}"/>
-    <hyperlink ref="J29" r:id="rId19" xr:uid="{D5042539-9629-4DAD-A5DE-1A0DB1EDA443}"/>
-    <hyperlink ref="J17" r:id="rId20" xr:uid="{5D9BDD0B-66A9-48F4-AB3E-E7DF27C9C69E}"/>
-    <hyperlink ref="J25" r:id="rId21" xr:uid="{6647EFF2-FEDE-4CF5-B940-BC01E6A58DBF}"/>
+    <hyperlink ref="J9" r:id="rId6" xr:uid="{11F395D0-5504-489D-8656-EE1A54C23DDA}"/>
+    <hyperlink ref="J11" r:id="rId7" xr:uid="{00E66CDD-5400-4FE1-89A5-0B9266D05039}"/>
+    <hyperlink ref="J12" r:id="rId8" xr:uid="{9BE63AE3-6695-42BA-8E8F-2E98D962A63D}"/>
+    <hyperlink ref="J26" r:id="rId9" xr:uid="{E0D90F7C-094F-47C4-9689-4F38ABBDE890}"/>
+    <hyperlink ref="J10" r:id="rId10" xr:uid="{DE42A9A5-39BC-4817-B668-4848AF823537}"/>
+    <hyperlink ref="J13" r:id="rId11" xr:uid="{6CD35D92-F3FD-492E-917B-74821F76AA6E}"/>
+    <hyperlink ref="J14" r:id="rId12" xr:uid="{5D0CD5F4-CF09-4B0B-9EF4-A72BAD63B893}"/>
+    <hyperlink ref="J15" r:id="rId13" xr:uid="{9FFA7A70-825A-4AE7-AA84-83662A62C65C}"/>
+    <hyperlink ref="J16" r:id="rId14" xr:uid="{C6EE7D64-B7D3-498D-8A0C-182E49FF9909}"/>
+    <hyperlink ref="J17" r:id="rId15" xr:uid="{CA602DEC-6055-4FEF-B8CF-5C4E7CA097D8}"/>
+    <hyperlink ref="K17" r:id="rId16" xr:uid="{0DA2FBD3-91BB-42D2-86F2-26BC53ADEF37}"/>
+    <hyperlink ref="J22" r:id="rId17" xr:uid="{5ECE52DB-8AB3-4E55-AAFC-EE48888ABB4E}"/>
+    <hyperlink ref="J30" r:id="rId18" xr:uid="{9B9D0334-4414-41B1-AFC9-C38746C7F6AB}"/>
+    <hyperlink ref="J31" r:id="rId19" xr:uid="{D5042539-9629-4DAD-A5DE-1A0DB1EDA443}"/>
+    <hyperlink ref="J18" r:id="rId20" xr:uid="{5D9BDD0B-66A9-48F4-AB3E-E7DF27C9C69E}"/>
+    <hyperlink ref="J27" r:id="rId21" xr:uid="{6647EFF2-FEDE-4CF5-B940-BC01E6A58DBF}"/>
+    <hyperlink ref="J32" r:id="rId22" xr:uid="{17D9DC54-AFDB-4DD2-9792-EE9CDD5DAAE8}"/>
+    <hyperlink ref="J19" r:id="rId23" xr:uid="{4A149A0D-9E5C-41BA-87B3-BCE72F7AC578}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId22"/>
+  <pageSetup orientation="portrait" r:id="rId24"/>
 </worksheet>
 </file>
--- a/Components.xlsx
+++ b/Components.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nuwildcat-my.sharepoint.com/personal/org0708_ads_northwestern_edu/Documents/Northwestern/Extracurricular/hardware/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="422" documentId="11_F25DC773A252ABDACC10485809DA5EF65ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83068B3B-37BD-4A00-A6D2-9BFAC2366ABF}"/>
+  <xr:revisionPtr revIDLastSave="476" documentId="11_F25DC773A252ABDACC10485809DA5EF65ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9FC8C7AA-83EF-49CA-8560-B87A4D937969}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="12196" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ECVT" sheetId="1" r:id="rId1"/>
+    <sheet name="ECVT Big Things" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="156">
   <si>
     <t>Component</t>
   </si>
@@ -436,13 +437,70 @@
   </si>
   <si>
     <t xml:space="preserve">R7 / R1 / R8 </t>
+  </si>
+  <si>
+    <t>311-10KGRCT-ND</t>
+  </si>
+  <si>
+    <t>RC0603JR-0710KL</t>
+  </si>
+  <si>
+    <t>RES 10K OHM 5% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>Through hole</t>
+  </si>
+  <si>
+    <t>13-UDD32C03L01CT-ND</t>
+  </si>
+  <si>
+    <t>UDD32C03L01</t>
+  </si>
+  <si>
+    <t>TVS DIODE 3.3VWM 15VC SOD323</t>
+  </si>
+  <si>
+    <t>Surface Mount SOD-323</t>
+  </si>
+  <si>
+    <t>TVS (3.3V)</t>
+  </si>
+  <si>
+    <t>D2/3/4/5/6</t>
+  </si>
+  <si>
+    <t>TVS (5V)</t>
+  </si>
+  <si>
+    <t>D7/D8</t>
+  </si>
+  <si>
+    <t>1727-PESD5V0S1BA-QFCT-ND</t>
+  </si>
+  <si>
+    <t>PESD5V0S1BA-QF</t>
+  </si>
+  <si>
+    <t>14V Clamp 12A (8/20µs) Ipp Tvs Diode Surface Mount SOD-323</t>
+  </si>
+  <si>
+    <t>TVS (Battery)</t>
+  </si>
+  <si>
+    <t>TVS DIODE 16VWM 26VC P600</t>
+  </si>
+  <si>
+    <t>SLD16U-017</t>
+  </si>
+  <si>
+    <t>F5677CT-ND</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -473,26 +531,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color theme="1"/>
+      <sz val="11"/>
+      <color rgb="FF444444"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF444444"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF444444"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -505,11 +551,43 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -519,26 +597,43 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -820,700 +915,986 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:L33"/>
+  <dimension ref="A2:L36"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="14.19921875" customWidth="1"/>
-    <col min="3" max="3" width="16.86328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.86328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.86328125" customWidth="1"/>
-    <col min="5" max="5" width="14.19921875" customWidth="1"/>
+    <col min="5" max="5" width="29.19921875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="31.1328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.1328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="52.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="11" width="14.19921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B2" t="s">
+      <c r="A2" s="16"/>
+      <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J2" t="s">
-        <v>7</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="J2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" s="5" t="s">
         <v>8</v>
       </c>
+      <c r="L2" s="6"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="H3" s="1"/>
+      <c r="A3" s="16"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="4">
         <v>2</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="K4" t="s">
-        <v>68</v>
-      </c>
-      <c r="L4" t="s">
+      <c r="K4" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="L4" s="6" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B5" t="s">
+      <c r="A5" s="16"/>
+      <c r="B5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="3" t="s">
+      <c r="D5" s="8"/>
+      <c r="E5" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="4">
         <v>2</v>
       </c>
-      <c r="J5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K5" t="s">
-        <v>68</v>
-      </c>
+      <c r="J5" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="L5" s="6"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B6" t="s">
+      <c r="A6" s="16"/>
+      <c r="B6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="4">
         <v>2</v>
       </c>
-      <c r="J6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K6" t="s">
-        <v>68</v>
-      </c>
+      <c r="J6" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="L6" s="6"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A7" s="16"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="6"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="D8" s="1"/>
+      <c r="A8" s="16"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="6"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="4">
         <v>2</v>
       </c>
-      <c r="J9" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K9" t="s">
-        <v>68</v>
-      </c>
+      <c r="J9" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="L9" s="6"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B10" t="s">
+      <c r="A10" s="16"/>
+      <c r="B10" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="4">
         <v>2</v>
       </c>
-      <c r="J10" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K10" t="s">
-        <v>68</v>
-      </c>
+      <c r="J10" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="L10" s="6"/>
     </row>
     <row r="11" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="B11" t="s">
+      <c r="A11" s="16"/>
+      <c r="B11" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="H11" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="4">
         <v>2</v>
       </c>
-      <c r="J11" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K11" t="s">
-        <v>68</v>
-      </c>
+      <c r="J11" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="L11" s="6"/>
     </row>
     <row r="12" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="B12" t="s">
+      <c r="A12" s="16"/>
+      <c r="B12" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="G12" s="15"/>
+      <c r="H12" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="4">
         <v>4</v>
       </c>
-      <c r="J12" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K12" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="B13" t="s">
+      <c r="J12" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="L12" s="6"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A13" s="16"/>
+      <c r="B13" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="G13" s="10" t="s">
+      <c r="G13" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="4">
         <v>2</v>
       </c>
-      <c r="J13" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K13" t="s">
-        <v>68</v>
-      </c>
+      <c r="J13" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="L13" s="6"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B14" t="s">
+      <c r="A14" s="16"/>
+      <c r="B14" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H14" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="4">
         <v>2</v>
       </c>
-      <c r="J14" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K14" t="s">
-        <v>68</v>
-      </c>
+      <c r="J14" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="L14" s="6"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B15" t="s">
+      <c r="A15" s="16"/>
+      <c r="B15" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="H15" t="s">
+      <c r="G15" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="H15" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="4">
         <v>2</v>
       </c>
-      <c r="J15" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K15" t="s">
-        <v>68</v>
-      </c>
+      <c r="J15" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="L15" s="6"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B16" t="s">
+      <c r="A16" s="16"/>
+      <c r="B16" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="15">
         <v>603</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H16" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="4">
         <v>4</v>
       </c>
-      <c r="J16" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K16" t="s">
-        <v>68</v>
-      </c>
+      <c r="J16" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="L16" s="6"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B17" t="s">
+      <c r="A17" s="16"/>
+      <c r="B17" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="H17" t="s">
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="J17" s="4" t="s">
+      <c r="I17" s="4"/>
+      <c r="J17" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="K17" s="4" t="s">
+      <c r="K17" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="L17" t="s">
+      <c r="L17" s="6" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B18" t="s">
+      <c r="A18" s="16"/>
+      <c r="B18" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="15">
         <v>603</v>
       </c>
-      <c r="H18" t="s">
+      <c r="H18" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="4">
         <v>4</v>
       </c>
-      <c r="J18" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K18" t="s">
-        <v>68</v>
-      </c>
+      <c r="J18" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="L18" s="6"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B19" t="s">
+      <c r="A19" s="16"/>
+      <c r="B19" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="15">
         <v>603</v>
       </c>
-      <c r="H19" t="s">
+      <c r="H19" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="4">
         <v>12</v>
       </c>
-      <c r="J19" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K19" t="s">
-        <v>68</v>
-      </c>
+      <c r="J19" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="L19" s="6"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A20" s="16"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="6"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A21" s="16"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="4"/>
+      <c r="L21" s="6"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="G22" t="s">
+      <c r="G22" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="H22" t="s">
+      <c r="H22" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="4">
         <v>2</v>
       </c>
-      <c r="J22" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K22" t="s">
+      <c r="J22" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="K22" s="4" t="s">
         <v>124</v>
       </c>
+      <c r="L22" s="6"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A23" s="16"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="6"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A24" s="16"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="6"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A25" s="16"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="6"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="4">
         <v>2223</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="H26" t="s">
+      <c r="G26" s="15"/>
+      <c r="H26" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="4">
         <v>2</v>
       </c>
-      <c r="J26" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K26" t="s">
-        <v>68</v>
-      </c>
+      <c r="J26" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="L26" s="6"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B27" t="s">
+      <c r="A27" s="16"/>
+      <c r="B27" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="4">
         <v>971110155</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F27" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="H27" t="s">
+      <c r="G27" s="15"/>
+      <c r="H27" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="4">
         <v>8</v>
       </c>
-      <c r="J27" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K27" t="s">
+      <c r="J27" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="K27" s="4" t="s">
         <v>124</v>
       </c>
+      <c r="L27" s="6"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A28" s="16"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="6"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A29" s="16"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="6"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F30" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="G30" t="s">
+      <c r="G30" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="H30" t="s">
+      <c r="H30" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="I30">
+      <c r="I30" s="4">
         <v>10</v>
       </c>
-      <c r="J30" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K30" t="s">
-        <v>68</v>
-      </c>
+      <c r="J30" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="L30" s="6"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B31" t="s">
+      <c r="A31" s="16"/>
+      <c r="B31" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F31" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="G31">
+      <c r="G31" s="15">
         <v>805</v>
       </c>
-      <c r="H31" t="s">
+      <c r="H31" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="I31">
+      <c r="I31" s="4">
         <v>3</v>
       </c>
-      <c r="J31" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K31" t="s">
-        <v>68</v>
-      </c>
+      <c r="J31" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="L31" s="6"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B32" t="s">
+      <c r="A32" s="16"/>
+      <c r="B32" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E32" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="F32" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="G32" s="3">
+      <c r="G32" s="13">
         <v>805</v>
       </c>
-      <c r="H32" t="s">
+      <c r="H32" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="I32">
+      <c r="I32" s="4">
         <v>10</v>
       </c>
-      <c r="J32" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K32" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B33" t="s">
+      <c r="J32" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="L32" s="6"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A33" s="16"/>
+      <c r="B33" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="I33">
+      <c r="D33" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G33" s="15">
+        <v>603</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="I33" s="4">
         <v>10</v>
       </c>
-      <c r="K33" t="s">
+      <c r="J33" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="K33" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="L33" s="6"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A34" s="3"/>
+      <c r="B34" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="I34" s="17">
+        <v>15</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="B35" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="D35" t="s">
+        <v>150</v>
+      </c>
+      <c r="E35" t="s">
+        <v>149</v>
+      </c>
+      <c r="F35" t="s">
+        <v>40</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H35" t="s">
+        <v>151</v>
+      </c>
+      <c r="I35" s="17">
+        <v>4</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K35" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="B36" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="D36" t="s">
+        <v>154</v>
+      </c>
+      <c r="E36" t="s">
+        <v>155</v>
+      </c>
+      <c r="F36" t="s">
+        <v>20</v>
+      </c>
+      <c r="H36" t="s">
+        <v>153</v>
+      </c>
+      <c r="I36" s="17">
+        <v>2</v>
+      </c>
+      <c r="K36" s="4" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1542,8 +1923,20 @@
     <hyperlink ref="J27" r:id="rId21" xr:uid="{6647EFF2-FEDE-4CF5-B940-BC01E6A58DBF}"/>
     <hyperlink ref="J32" r:id="rId22" xr:uid="{17D9DC54-AFDB-4DD2-9792-EE9CDD5DAAE8}"/>
     <hyperlink ref="J19" r:id="rId23" xr:uid="{4A149A0D-9E5C-41BA-87B3-BCE72F7AC578}"/>
+    <hyperlink ref="J33" r:id="rId24" xr:uid="{67A01198-F3DD-4A7F-92EA-5538F5EF7EAF}"/>
+    <hyperlink ref="J34" r:id="rId25" xr:uid="{2FD1E941-5898-47F8-81BA-A07263032890}"/>
+    <hyperlink ref="J35" r:id="rId26" xr:uid="{425F45FE-392A-4788-B756-C044A3B79F62}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId24"/>
+  <pageSetup orientation="portrait" r:id="rId27"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DAA8975-C2A1-4D57-B107-F3ABD1EC444D}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Components.xlsx
+++ b/Components.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nuwildcat-my.sharepoint.com/personal/org0708_ads_northwestern_edu/Documents/Northwestern/Extracurricular/hardware/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="476" documentId="11_F25DC773A252ABDACC10485809DA5EF65ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9FC8C7AA-83EF-49CA-8560-B87A4D937969}"/>
+  <xr:revisionPtr revIDLastSave="484" documentId="11_F25DC773A252ABDACC10485809DA5EF65ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9655D358-8750-4C2F-B430-42E3F9E28E82}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="12196" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="160">
   <si>
     <t>Component</t>
   </si>
@@ -494,6 +494,18 @@
   </si>
   <si>
     <t>F5677CT-ND</t>
+  </si>
+  <si>
+    <t>THT: Axial P600</t>
+  </si>
+  <si>
+    <t>D9</t>
+  </si>
+  <si>
+    <t>Limit Switch</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/aratas-formerly-omron-components-/D2AW-ER073H-R/11313096?utm_source=chatgpt.com&amp;oppcref=195339cc-3c96-4fbd-aac6-31664550a659</t>
   </si>
 </sst>
 </file>
@@ -1082,16 +1094,36 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7" s="16"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
+      <c r="B7" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="D7" t="s">
+        <v>154</v>
+      </c>
+      <c r="E7" t="s">
+        <v>155</v>
+      </c>
+      <c r="F7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H7" t="s">
+        <v>153</v>
+      </c>
+      <c r="I7" s="17">
+        <v>2</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>68</v>
+      </c>
       <c r="L7" s="6"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.45">
@@ -1538,16 +1570,36 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A23" s="16"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4"/>
+      <c r="B23" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="D23" t="s">
+        <v>150</v>
+      </c>
+      <c r="E23" t="s">
+        <v>149</v>
+      </c>
+      <c r="F23" t="s">
+        <v>40</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H23" t="s">
+        <v>151</v>
+      </c>
+      <c r="I23" s="17">
+        <v>4</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>68</v>
+      </c>
       <c r="L23" s="6"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.45">
@@ -1843,59 +1895,12 @@
         <v>68</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B35" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="C35" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="D35" t="s">
-        <v>150</v>
-      </c>
-      <c r="E35" t="s">
-        <v>149</v>
-      </c>
-      <c r="F35" t="s">
-        <v>40</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="H35" t="s">
-        <v>151</v>
-      </c>
-      <c r="I35" s="17">
-        <v>4</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="K35" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B36" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="D36" t="s">
-        <v>154</v>
-      </c>
-      <c r="E36" t="s">
-        <v>155</v>
-      </c>
-      <c r="F36" t="s">
-        <v>20</v>
+      <c r="B36" t="s">
+        <v>158</v>
       </c>
       <c r="H36" t="s">
-        <v>153</v>
-      </c>
-      <c r="I36" s="17">
-        <v>2</v>
-      </c>
-      <c r="K36" s="4" t="s">
-        <v>68</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -1925,10 +1930,11 @@
     <hyperlink ref="J19" r:id="rId23" xr:uid="{4A149A0D-9E5C-41BA-87B3-BCE72F7AC578}"/>
     <hyperlink ref="J33" r:id="rId24" xr:uid="{67A01198-F3DD-4A7F-92EA-5538F5EF7EAF}"/>
     <hyperlink ref="J34" r:id="rId25" xr:uid="{2FD1E941-5898-47F8-81BA-A07263032890}"/>
-    <hyperlink ref="J35" r:id="rId26" xr:uid="{425F45FE-392A-4788-B756-C044A3B79F62}"/>
+    <hyperlink ref="J23" r:id="rId26" xr:uid="{425F45FE-392A-4788-B756-C044A3B79F62}"/>
+    <hyperlink ref="J7" r:id="rId27" xr:uid="{01E3DB93-1E8A-4AE0-9C00-FFD6719283AA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId27"/>
+  <pageSetup orientation="portrait" r:id="rId28"/>
 </worksheet>
 </file>
 
